--- a/docs/downloads/05/tbl_agri_equip_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_marovoay_madiromiongana.xlsx
@@ -418,12 +418,6 @@
           <t>Arrosoir/Sceau</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -436,12 +430,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -454,12 +442,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -490,12 +472,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -544,12 +520,6 @@
           <t>Corde (ex : servant pour</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -598,12 +568,6 @@
           <t>Filet</t>
         </is>
       </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -688,12 +652,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -706,12 +664,6 @@
           <t>Râteau, fourche</t>
         </is>
       </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -724,12 +676,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -742,12 +688,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -778,12 +718,6 @@
           <t>Tracteur</t>
         </is>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -845,12 +779,6 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -863,12 +791,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C29">
-        <v>3</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -899,12 +821,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -935,12 +851,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -953,12 +863,6 @@
           <t>Canne planteuse</t>
         </is>
       </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1007,12 +911,6 @@
           <t>Corde (ex : servant pour</t>
         </is>
       </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1043,12 +941,6 @@
           <t>Décortiqueur / dépailleur</t>
         </is>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1115,12 +1007,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C43">
-        <v>4</v>
-      </c>
-      <c r="D43">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1169,12 +1055,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C46">
-        <v>4</v>
-      </c>
-      <c r="D46">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1205,12 +1085,6 @@
           <t>Pompe hydraulique</t>
         </is>
       </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1223,12 +1097,6 @@
           <t>Pulvérisateur</t>
         </is>
       </c>
-      <c r="C49">
-        <v>3</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1241,12 +1109,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C50">
-        <v>4</v>
-      </c>
-      <c r="D50">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1259,12 +1121,6 @@
           <t>Râteau, fourche</t>
         </is>
       </c>
-      <c r="C51">
-        <v>4</v>
-      </c>
-      <c r="D51">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1295,12 +1151,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53">
-        <v>0</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1330,12 +1180,6 @@
         <is>
           <t>Tracteur</t>
         </is>
-      </c>
-      <c r="C55">
-        <v>2</v>
-      </c>
-      <c r="D55">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
